--- a/www/download/COUNTRY.CHN.zdW16.xlsx
+++ b/www/download/COUNTRY.CHN.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>8.27855690333697</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>8.27691240338643</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>8.27704939102898</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>8.27698087962518</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>8.27691237067746</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>8.19336337514046</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>7.97270138586024</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>7.60531450957138</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>6.94589150908069</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>6.83139434388019</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>6.76956399844481</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1.883</t>
+          <t>6.46011522202256</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>6.31229445096852</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2.549</t>
+          <t>6.19524946611821</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.14337404053866</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>719.604</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>728.107</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>737.284</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>744.531</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>752.281</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>759.77</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>765.353</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>770.887</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>777.013</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>784.924</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>784.663</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>840.443</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>854.216</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>857.826</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>858.367</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>271.888</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>281.049</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>290.755</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>299.897</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>309.413</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>318.997</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>327.893</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>336.87</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>346.221</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>356.505</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>363.142</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>396.126</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>409.87</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>418.859</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>426.36</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1281154.752</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1358661.991</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1430092.97</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1472458.079</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1501021.793</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1509876.006</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1494135.694</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1519893.748</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1568479.449</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1591354.705</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1597046.567</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1736502.387</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1770099.919</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1784985.375</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1790192.448</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>484058.712</t>
+          <t>1863347131814.51</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>524443.508</t>
+          <t>1839258523647.5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>563971.475</t>
+          <t>1847594287195.14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>593106.096</t>
+          <t>1894288740499.86</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>617370.28</t>
+          <t>1963933658212.81</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>633936.541</t>
+          <t>2047704116761.31</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>640117.6</t>
+          <t>2208680433085.51</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>664178.389</t>
+          <t>2311860590197.13</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>698883.052</t>
+          <t>2430776377973.76</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>722777.373</t>
+          <t>2552047439680.91</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>739113.132</t>
+          <t>2532383352978.52</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>818465.66</t>
+          <t>2795077497272.42</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>849329.316</t>
+          <t>2867741555476.54</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>871572.643</t>
+          <t>2898221651989.22</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>889206.516</t>
+          <t>2842915641139.4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>459402381013.207</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>468867323916.257</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>487444975850.884</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>473078315806.158</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>472763870541.989</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>454477761525.934</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>465190228292.245</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>454493009948.474</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>497256419610.902</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>527731952185.948</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>527850196630.269</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>556146892408.826</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>586864795480.236</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>569731567947.354</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>571300313494.568</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>20488158.5169542</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>18739149.2076749</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>17608725.1516522</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>16070284.7033303</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>13914682.2470571</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>12072433.854582</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>10779120.4405942</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>8632843.67772921</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>7106693.71162829</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>6730216.23710172</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>5716485.30517547</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4986669.70009591</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4480529.81994122</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>3963869.37072483</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>3616790.87718501</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>9024730.33983812</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8916639.80458001</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>9130313.74480771</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>9793974.89406727</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>10816207.6707489</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>11667836.1960883</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>12783724.776663</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>14649704.4038912</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>16554806.6059185</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>15291298.6472632</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>16850404.1337438</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>19493552.0467102</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>19153069.438815</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>18812379.3794457</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>18511590.9689812</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>16903054.9779685</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>16440231.964279</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>16636219.1083225</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>18569601.9558345</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>21216456.6564582</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>23892990.9433805</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>27232830.1592678</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>31976036.7728741</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>36668923.2773928</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>35183455.1650332</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>38572104.8517201</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>45392672.7970682</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>45492964.064684</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>45709903.1242978</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>44994162.7152157</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.0536704470912386</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.118532857439535</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.156995154814429</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.253716512145182</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.305874492651072</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.39486811963009</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.376034062673678</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.461361064525796</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.405478188308024</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.369591835308116</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.40023274832439</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.471671731557074</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.447231666100639</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.529795243741759</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.556460753391576</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.27855690333697</t>
+          <t>1689.67444396527</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.27691240338643</t>
+          <t>1668.27331293641</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.27704939102898</t>
+          <t>1676.47928211301</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8.27698087962518</t>
+          <t>1577.46879182924</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8.27691237067746</t>
+          <t>1527.93710743026</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>8.19336337514046</t>
+          <t>1424.70898116678</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7.97270138586024</t>
+          <t>1418.72740651192</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>7.60531450957138</t>
+          <t>1349.16444031964</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6.94589150908069</t>
+          <t>1436.23799957726</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6.83139434388019</t>
+          <t>1480.29495651065</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>6.76956399844481</t>
+          <t>1453.56490596472</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>6.46011522202256</t>
+          <t>1403.96461351544</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>6.31229445096852</t>
+          <t>1431.83139474307</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>6.19524946611821</t>
+          <t>1360.19875111353</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>6.14337404053866</t>
+          <t>1339.94927016706</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>-81352993447.03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>-77712556932.0881</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>-87293987819.8632</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>-105739273293.816</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.924</t>
+          <t>-124724390286.176</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-144250969773.278</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>-152348223501.615</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>-151714095170.218</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.158</t>
+          <t>-133081282546.489</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.479</t>
+          <t>-102642425463.984</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>3.036</t>
+          <t>-101828783351.361</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>3.897</t>
+          <t>-98502296700.1527</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>4.577</t>
+          <t>-77103334787.5533</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>5.159</t>
+          <t>-59361489246.4761</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>5.666</t>
+          <t>-34302337566.8022</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>-84417452565.592</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>-81398839726.0452</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>-91775204411.8496</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>-109988859671.095</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.924</t>
+          <t>-128895616920.421</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-148495351239.676</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>-157203240512.671</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>-156708413355.734</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.158</t>
+          <t>-139142662312.311</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.479</t>
+          <t>-109591044665.227</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>3.036</t>
+          <t>-110025962502.394</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>3.897</t>
+          <t>-108610869692.376</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>4.577</t>
+          <t>-88037216654.5586</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>5.159</t>
+          <t>-67477921762.3247</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>5.666</t>
+          <t>-42070969300.2425</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.994</t>
+          <t>3064459118.56199</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.358</t>
+          <t>3686282793.95713</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.788</t>
+          <t>4481216591.98638</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.422</t>
+          <t>4249586377.27891</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5.326</t>
+          <t>4171226634.24402</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>6.376</t>
+          <t>4244381466.39846</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>7.636</t>
+          <t>4855017011.05612</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>9.346</t>
+          <t>4994318185.51669</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>12.592</t>
+          <t>6061379765.8219</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>14.292</t>
+          <t>6948619201.24384</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>17.111</t>
+          <t>8197179151.03264</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>21.877</t>
+          <t>10108572992.2237</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>10933881867.0054</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>29.478</t>
+          <t>8116432515.84852</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>32.899</t>
+          <t>7768631733.44023</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.253</t>
+          <t>1780.36002681152</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.521</t>
+          <t>1866.01851570889</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.812</t>
+          <t>1939.67840655153</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4.456</t>
+          <t>1977.69867171003</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5.438</t>
+          <t>1995.29409496824</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>6.707</t>
+          <t>1987.28113758021</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.178</t>
+          <t>1952.21723700909</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>10.654</t>
+          <t>1971.61638272585</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>2018.60118162499</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>15.037</t>
+          <t>2027.39988628477</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>18.054</t>
+          <t>2035.32918314686</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>22.609</t>
+          <t>2066.17503381713</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>25.593</t>
+          <t>2072.19173498921</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>29.233</t>
+          <t>2080.82557999697</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>31.745</t>
+          <t>2085.57845055072</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.198</t>
+          <t>1780.36002681152</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1866.01851570889</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1939.67840655153</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>1977.69867171003</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.932</t>
+          <t>1995.29409496824</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.257</t>
+          <t>1987.28113758021</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.713</t>
+          <t>1952.21723700909</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>3.495</t>
+          <t>1971.61638272585</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4.521</t>
+          <t>2018.60118162499</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>2027.39988628477</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>5.931</t>
+          <t>2035.32918314686</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>7.363</t>
+          <t>2066.17503381713</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>8.319</t>
+          <t>2072.19173498921</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>2080.82557999697</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>10.284</t>
+          <t>2085.57845055072</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>261938.018347437</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>280419.776941541</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>345007.298581019</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>461968.459632732</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>632557.40360393</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>806873.985656646</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1027619.28812731</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1304801.79860809</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1540785.17084099</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1293515.99451997</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1697752.27422866</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2037785.27696229</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2156117.46640958</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2293013.70422638</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2425464.4149329</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>123672329567.737</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>123774565336.157</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>141737970550.898</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>175392012696.057</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>211040586711.601</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>241872128885.773</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>265021308524.824</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>272517640918.772</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>261242361421.561</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>213708253359.93</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>235250128770.759</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>253543861159.563</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>243336437522.966</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>235344907877.996</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>225324203798.176</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>220558.903536225</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>238471.973188644</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>289345.805299956</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>398624.650055453</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>542305.951931379</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>636852.598601152</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>765258.47093438</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>924493.15346435</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>1100033.98775197</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>984359.709124691</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1358267.11517569</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1704024.77564393</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1748573.32597829</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1863450.36728005</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1842837.00475207</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1281154.752</t>
+          <t>36660539835.9654</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1358661.991</t>
+          <t>40091540800.3919</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1430092.97</t>
+          <t>46471668453.8819</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1472458.079</t>
+          <t>61100706442.8884</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1501021.793</t>
+          <t>75213116457.4516</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1509876.006</t>
+          <t>78650314155.0601</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1494135.694</t>
+          <t>86105421043.641</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1519893.748</t>
+          <t>87780799104.7996</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1568479.449</t>
+          <t>94748260303.5949</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1591354.705</t>
+          <t>84740641238.5214</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1597046.567</t>
+          <t>107651874402.825</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1736502.387</t>
+          <t>131057276308.302</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1770099.919</t>
+          <t>136751566810.022</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1784985.375</t>
+          <t>144599196595.783</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1790192.448</t>
+          <t>148863489051.033</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>484058.712</t>
+          <t>41379.1148112115</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>524443.508</t>
+          <t>41947.8037528966</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>563971.475</t>
+          <t>55661.4932810628</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>593106.096</t>
+          <t>63343.8095772788</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>617370.28</t>
+          <t>90251.4516725503</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>633936.541</t>
+          <t>170021.387055494</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>640117.6</t>
+          <t>262360.817192932</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>664178.389</t>
+          <t>380308.645143737</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>698883.052</t>
+          <t>440751.183089016</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>722777.373</t>
+          <t>309156.285395284</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>739113.132</t>
+          <t>339485.159052967</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>818465.66</t>
+          <t>333760.501318356</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>849329.316</t>
+          <t>407544.140431294</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>871572.643</t>
+          <t>429563.336946327</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>889206.516</t>
+          <t>582627.41018083</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2071059.115</t>
+          <t>87011789731.7719</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2027749.379</t>
+          <t>83683024535.7655</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2027948.036</t>
+          <t>95266302097.0165</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2075980.695</t>
+          <t>114291306253.169</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2151509.272</t>
+          <t>135827470254.149</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2256495.604</t>
+          <t>163221814730.713</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2428086.633</t>
+          <t>178915887481.183</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2527290.885</t>
+          <t>184736841813.973</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2685750.325</t>
+          <t>166494101117.966</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2852439.68</t>
+          <t>128967612121.409</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2809953.338</t>
+          <t>127598254367.934</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>3122025.905</t>
+          <t>122486584851.261</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>3236448.452</t>
+          <t>106584870712.944</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>3283111.799</t>
+          <t>90745711282.2128</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2842915.641</t>
+          <t>76460714747.1429</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>16.828</t>
+          <t>854042.305133276</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16.319</t>
+          <t>928727.79418407</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16.418</t>
+          <t>1008001.60077362</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18.292</t>
+          <t>1129248.95563351</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>1340976.65686878</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>23.602</t>
+          <t>1562777.21845455</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>26.832</t>
+          <t>1851357.58971296</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>31.529</t>
+          <t>2339648.29181658</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>36.369</t>
+          <t>3014636.28791816</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>35.153</t>
+          <t>3247845.09471929</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>38.363</t>
+          <t>3859811.67370404</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>45.261</t>
+          <t>4804492.46312296</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>45.721</t>
+          <t>5357776.15435154</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>46.337</t>
+          <t>5947785.36677478</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>44.994</t>
+          <t>6440149.89963705</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>994861.9</t>
+          <t>0.203692853704925</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>997553.185</t>
+          <t>0.201382393441097</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1013999.359</t>
+          <t>0.196693507832855</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>999085.301</t>
+          <t>0.193068817839001</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1001218.754</t>
+          <t>0.189294371029279</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>999970.086</t>
+          <t>0.187764851932626</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1036806.039</t>
+          <t>0.191489619999708</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1059170.482</t>
+          <t>0.204007684853332</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1097415.175</t>
+          <t>0.187695575588849</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1109161.092</t>
+          <t>0.175734323611965</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1106283.494</t>
+          <t>0.169168026701164</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1200325.632</t>
+          <t>0.158430258590101</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1207352.703</t>
+          <t>0.146270302858389</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1192792.842</t>
+          <t>0.14321254966555</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1169638.2</t>
+          <t>0.140374096487051</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8.083</t>
+          <t>588648.261561042</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8.028</t>
+          <t>648537.417706858</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8.209</t>
+          <t>708806.495508411</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8.803</t>
+          <t>787189.110805554</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>9.754</t>
+          <t>923516.897971014</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10.459</t>
+          <t>1059897.96776983</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>11.458</t>
+          <t>1251019.71548612</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>13.214</t>
+          <t>1588322.70451862</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>14.861</t>
+          <t>2157847.77481442</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>13.669</t>
+          <t>2478568.29858374</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>15.103</t>
+          <t>3036441.33262075</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>17.402</t>
+          <t>3896981.0192003</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>17.056</t>
+          <t>4577126.62759297</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>16.835</t>
+          <t>5158719.31637214</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>18.512</t>
+          <t>5665835.26711</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>502613.91</t>
+          <t>588648.261440248</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>509149.185</t>
+          <t>648537.417706858</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>527058.424</t>
+          <t>708806.495508411</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>510059.107</t>
+          <t>787189.110926371</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>508734.913</t>
+          <t>923516.897971014</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>490159.689</t>
+          <t>1059897.96776983</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>499655.154</t>
+          <t>1251019.71548612</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>484670.881</t>
+          <t>1588322.7047816</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>534315.695</t>
+          <t>2157847.77625412</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>570917.195</t>
+          <t>2478568.3015114</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>568982.504</t>
+          <t>3036441.33114355</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>603629.121</t>
+          <t>3896981.0192003</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>640766.772</t>
+          <t>4577126.62759297</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>623564.781</t>
+          <t>5158719.31798628</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>571300.313</t>
+          <t>5665835.26711</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>2993742.86980939</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3358259.88283325</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3787643.71776461</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>4422157.31166924</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>5325574.17921317</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>6376393.7018432</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>7635752.34695555</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>9346399.27334974</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>12592008.0238074</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>14292423.3597335</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>17111423.3990992</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>21876816.7470749</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>25580489.5361577</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>29478137.609998</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>55.65</t>
+          <t>32898860.3425465</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>23.021</t>
+          <t>1109163.86570766</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20.843</t>
+          <t>1153816.65605986</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>19.461</t>
+          <t>1223284.68524949</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>17.711</t>
+          <t>1271141.65320255</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>1349759.74063459</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>13.357</t>
+          <t>1478037.03340391</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>11.894</t>
+          <t>1633268.63422483</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>9.477</t>
+          <t>1782213.29766099</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>7.913</t>
+          <t>1995887.46387921</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>7.602</t>
+          <t>2165414.0577308</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>6.413</t>
+          <t>2482967.03960229</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>5.641</t>
+          <t>2803147.01312853</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>5.123</t>
+          <t>3131859.45936727</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>4.546</t>
+          <t>3363197.49428672</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>3.617</t>
+          <t>3633957.83455807</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1109163.86578011</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1153816.65605986</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1223284.68524949</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1271141.65304819</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1349759.74063459</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1478037.03336184</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1633268.634196</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1782213.29772046</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1995887.4622481</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2165414.05512831</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2482967.04081023</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2803147.01312853</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>3131859.45936727</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>3363197.49315615</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>3633957.83455807</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>609804.028410245</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>676294.413002177</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>745004.929268195</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>853780.684462076</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1008101.21462393</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1197262.61929072</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1462167.31533039</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1906737.27747094</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2363464.19384793</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2511669.35189861</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2894705.73047374</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>3465949.73436733</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>3741665.95171963</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>4221639.24651976</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>4618147.79603863</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>484058712196.965</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>524443507580.079</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>563971475298.109</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>593106096064.014</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>617370279587.777</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>633936540633.373</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>640117599753.073</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>664178388837.835</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>698883051759.265</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>722777372945.087</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>739113131531.172</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>818465660151.383</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>849329315738.673</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>871572642855.397</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>889206516354.598</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1281154752206.01</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1358661990589.66</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1430092969802.58</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1472458078520.36</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1501021793160.33</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1509876005638.66</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1494135693822.33</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1519893747974.16</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1568479448756.43</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1591354704670.79</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1597046566584.14</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1736502387336.04</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1770099919453.61</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1784985374665.7</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1790192447816.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>994861900174.557</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>997553185289.72</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1013999359191.35</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>999085301380.989</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1001218754043.79</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>999970086166.46</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1036806039292.88</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1059170481631.55</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1097415174565.54</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1109161092311.59</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1106283493817.43</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1200325632096.01</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1207352703299.81</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1192792841732.42</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1169638200430.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>719604312</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>728107454</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>737283544</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>744531055</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>752280978</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>759769706</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>765353192</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>770887157</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>777013044</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>784923939</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>784662540</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>840443021</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>854216282</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>857825563</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>858367350</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>271888104.039201</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>281049466.103956</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>290755144.457565</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>299897099.870721</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>309413174.300806</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>318996909.217022</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>327892607.245785</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>336869988.836052</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>346221461.733545</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>356504593.807384</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>363141813.939117</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>396126004.21336</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>409870043.103466</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>418859058.266992</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>426359658.693153</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1281154752206.01</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1358661990589.66</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1430092969802.58</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1472458078520.36</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1501021793160.33</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1509876005638.66</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1494135693822.33</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1519893747974.16</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1568479448756.43</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1591354704670.79</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1597046566584.14</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1736502387336.04</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1770099919453.61</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1784985374665.7</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1790192447816.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>484058712196.965</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>524443507580.079</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>563971475298.109</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>593106096064.014</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>617370279587.777</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>633936540633.373</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>640117599753.073</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>664178388837.835</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>698883051759.265</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>722777372945.087</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>739113131531.172</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>818465660151.383</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>849329315738.673</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>871572642855.397</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>889206516354.598</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3253015.70227797</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3521177.91153665</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3812211.86576439</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>4455647.71315393</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>5437770.06408265</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>6707046.56430474</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>8177587.50590138</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>10654372.3158218</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>13689958.4413456</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>15036959.8810756</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>18053714.464996</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>22608922.70497</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>25593234.4224765</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>29232642.460012</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>31745102.4312362</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1198452.28731382</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1324831.83964957</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1453811.41873581</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1640969.79297211</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1931618.10305032</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2257160.588159</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2713187.017772</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>3495059.9684464</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>4521311.99515283</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>4990237.6414066</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>5931147.01080161</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>7362930.74985253</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>8318792.56141102</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>9380358.56434463</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>10283983.0468709</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4919624.03745587</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5396581.55777743</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>5988833.77341301</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>6718674.5767622</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>7491983.49042179</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>8408410.87669791</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>9368539.06279825</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>10234712.2328434</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>11758757.5018991</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>12759887.5674895</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>13992399.5353852</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>15839810.5692754</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>17635255.1185056</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>19306413.0707955</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>21206564.5748714</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
